--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127745519</v>
+        <v>127745525</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718552</v>
+        <v>718550</v>
       </c>
       <c r="R7" t="n">
-        <v>7109768</v>
+        <v>7109640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127745525</v>
+        <v>127745519</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718550</v>
+        <v>718552</v>
       </c>
       <c r="R8" t="n">
-        <v>7109640</v>
+        <v>7109768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B2" t="n">
-        <v>97327</v>
+        <v>58494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R2" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B3" t="n">
-        <v>58494</v>
+        <v>97327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R3" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127745525</v>
+        <v>127745519</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718550</v>
+        <v>718552</v>
       </c>
       <c r="R7" t="n">
-        <v>7109640</v>
+        <v>7109768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127745519</v>
+        <v>127745525</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718552</v>
+        <v>718550</v>
       </c>
       <c r="R8" t="n">
-        <v>7109768</v>
+        <v>7109640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127745516</v>
       </c>
       <c r="B3" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127745521</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127745520</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127745519</v>
+        <v>127745525</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718552</v>
+        <v>718550</v>
       </c>
       <c r="R7" t="n">
-        <v>7109768</v>
+        <v>7109640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127745525</v>
+        <v>127745519</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718550</v>
+        <v>718552</v>
       </c>
       <c r="R8" t="n">
-        <v>7109640</v>
+        <v>7109768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B2" t="n">
-        <v>58494</v>
+        <v>97336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R2" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B3" t="n">
-        <v>97333</v>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R3" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127745521</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127745523</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127745520</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127745525</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127745519</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127745524</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B2" t="n">
-        <v>97336</v>
+        <v>58503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R2" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B3" t="n">
-        <v>58497</v>
+        <v>97344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R3" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127745521</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127745523</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127745520</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127745525</v>
+        <v>127745519</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718550</v>
+        <v>718552</v>
       </c>
       <c r="R7" t="n">
-        <v>7109640</v>
+        <v>7109768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127745519</v>
+        <v>127745525</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718552</v>
+        <v>718550</v>
       </c>
       <c r="R8" t="n">
-        <v>7109768</v>
+        <v>7109640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>127745524</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B2" t="n">
-        <v>58503</v>
+        <v>97345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R2" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B3" t="n">
-        <v>97344</v>
+        <v>58503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R3" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127745521</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127745520</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127745519</v>
+        <v>127745525</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718552</v>
+        <v>718550</v>
       </c>
       <c r="R7" t="n">
-        <v>7109768</v>
+        <v>7109640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127745525</v>
+        <v>127745519</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718550</v>
+        <v>718552</v>
       </c>
       <c r="R8" t="n">
-        <v>7109640</v>
+        <v>7109768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B2" t="n">
-        <v>97345</v>
+        <v>58503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R2" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B3" t="n">
-        <v>58503</v>
+        <v>97345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R3" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B2" t="n">
-        <v>58503</v>
+        <v>97346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R2" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B3" t="n">
-        <v>97345</v>
+        <v>58503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R3" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127745521</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127745520</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127745519</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B2" t="n">
-        <v>97346</v>
+        <v>58503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R2" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B3" t="n">
-        <v>58503</v>
+        <v>97347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R3" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127745521</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127745520</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127745519</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B2" t="n">
-        <v>58503</v>
+        <v>97347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R2" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B3" t="n">
-        <v>97347</v>
+        <v>58503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R3" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B2" t="n">
-        <v>97347</v>
+        <v>58503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R2" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B3" t="n">
-        <v>58503</v>
+        <v>97347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R3" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127745512</v>
       </c>
       <c r="B2" t="n">
-        <v>58503</v>
+        <v>58504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127745516</v>
       </c>
       <c r="B3" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127745521</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127745523</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127745520</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127745525</v>
+        <v>127745519</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718550</v>
+        <v>718552</v>
       </c>
       <c r="R7" t="n">
-        <v>7109640</v>
+        <v>7109768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127745519</v>
+        <v>127745525</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718552</v>
+        <v>718550</v>
       </c>
       <c r="R8" t="n">
-        <v>7109768</v>
+        <v>7109640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>127745524</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B2" t="n">
-        <v>58504</v>
+        <v>97355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R2" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B3" t="n">
-        <v>97355</v>
+        <v>58504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R3" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 25986-2025 artfynd.xlsx
+++ b/artfynd/A 25986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127745516</v>
+        <v>127745512</v>
       </c>
       <c r="B2" t="n">
-        <v>97355</v>
+        <v>58516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718542</v>
+        <v>718648</v>
       </c>
       <c r="R2" t="n">
-        <v>7109724</v>
+        <v>7109743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127745512</v>
+        <v>127745516</v>
       </c>
       <c r="B3" t="n">
-        <v>58504</v>
+        <v>97448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718648</v>
+        <v>718542</v>
       </c>
       <c r="R3" t="n">
-        <v>7109743</v>
+        <v>7109724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127745521</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127745523</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127745520</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127745519</v>
+        <v>127745525</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718552</v>
+        <v>718550</v>
       </c>
       <c r="R7" t="n">
-        <v>7109768</v>
+        <v>7109640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127745525</v>
+        <v>127745519</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718550</v>
+        <v>718552</v>
       </c>
       <c r="R8" t="n">
-        <v>7109640</v>
+        <v>7109768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>127745524</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
